--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>121225934</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121226037</v>
+        <v>121226171</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,11 +1117,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1133,10 +1129,10 @@
         <v>618640</v>
       </c>
       <c r="R5" t="n">
-        <v>6662168</v>
+        <v>6662155</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1165,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,7 +1171,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1208,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121221578</v>
+        <v>121226037</v>
       </c>
       <c r="B6" t="n">
-        <v>56560</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1220,46 +1216,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618702</v>
+        <v>618640</v>
       </c>
       <c r="R6" t="n">
-        <v>6662175</v>
+        <v>6662168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1301,12 +1305,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,6 +1319,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1333,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121226171</v>
+        <v>121221578</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>56563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,53 +1350,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618640</v>
+        <v>618702</v>
       </c>
       <c r="R7" t="n">
-        <v>6662155</v>
+        <v>6662175</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1420,7 +1421,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,12 +1431,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,7 +1445,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>121222114</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121225934</v>
+        <v>121226171</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -983,11 +983,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -996,13 +992,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618662</v>
+        <v>618640</v>
       </c>
       <c r="R4" t="n">
-        <v>6662205</v>
+        <v>6662155</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,7 +1027,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,12 +1037,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121226171</v>
+        <v>121226037</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1113,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         <v>618640</v>
       </c>
       <c r="R5" t="n">
-        <v>6662155</v>
+        <v>6662168</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1204,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121226037</v>
+        <v>121221578</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>56563</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,54 +1216,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618640</v>
+        <v>618702</v>
       </c>
       <c r="R6" t="n">
-        <v>6662168</v>
+        <v>6662175</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1305,12 +1297,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,7 +1311,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121221578</v>
+        <v>121225934</v>
       </c>
       <c r="B7" t="n">
-        <v>56563</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,46 +1341,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618702</v>
+        <v>618662</v>
       </c>
       <c r="R7" t="n">
-        <v>6662175</v>
+        <v>6662205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,7 +1420,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1431,12 +1430,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1445,6 +1444,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121226171</v>
+        <v>121225934</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -983,7 +983,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -992,13 +996,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618640</v>
+        <v>618662</v>
       </c>
       <c r="R4" t="n">
-        <v>6662155</v>
+        <v>6662205</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,12 +1041,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1077,7 @@
         <v>121226037</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1329,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121225934</v>
+        <v>121226171</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,7 +1368,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1372,11 +1376,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618662</v>
+        <v>618640</v>
       </c>
       <c r="R7" t="n">
-        <v>6662205</v>
+        <v>6662155</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1466,7 +1466,7 @@
         <v>121222114</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>121225934</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>121226037</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>121226171</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>121222114</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>121225934</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>121226037</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>121221578</v>
       </c>
       <c r="B6" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>121226171</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>121222114</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -1074,10 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121226037</v>
+        <v>121221578</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>56566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,54 +1086,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618640</v>
+        <v>618702</v>
       </c>
       <c r="R5" t="n">
-        <v>6662168</v>
+        <v>6662175</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,12 +1167,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1181,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1208,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121221578</v>
+        <v>121226171</v>
       </c>
       <c r="B6" t="n">
-        <v>56566</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1220,49 +1211,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618702</v>
+        <v>618640</v>
       </c>
       <c r="R6" t="n">
-        <v>6662175</v>
+        <v>6662155</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1291,7 +1286,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1301,12 +1296,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,6 +1310,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1333,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121226171</v>
+        <v>121226037</v>
       </c>
       <c r="B7" t="n">
         <v>98098</v>
@@ -1368,7 +1364,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1376,7 +1372,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1388,10 +1388,10 @@
         <v>618640</v>
       </c>
       <c r="R7" t="n">
-        <v>6662155</v>
+        <v>6662168</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121225934</v>
+        <v>121221578</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>56567</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,54 +952,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618662</v>
+        <v>618702</v>
       </c>
       <c r="R4" t="n">
-        <v>6662205</v>
+        <v>6662175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1023,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,12 +1033,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1047,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1074,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121221578</v>
+        <v>121226171</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,49 +1077,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618702</v>
+        <v>618640</v>
       </c>
       <c r="R5" t="n">
-        <v>6662175</v>
+        <v>6662155</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,12 +1162,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,6 +1176,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1199,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121226171</v>
+        <v>121225934</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1234,7 +1230,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1242,7 +1238,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618640</v>
+        <v>618662</v>
       </c>
       <c r="R6" t="n">
-        <v>6662155</v>
+        <v>6662205</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,7 +1332,7 @@
         <v>121226037</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>121222114</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121221578</v>
+        <v>121226037</v>
       </c>
       <c r="B4" t="n">
-        <v>56567</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,46 +952,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618702</v>
+        <v>618640</v>
       </c>
       <c r="R4" t="n">
-        <v>6662175</v>
+        <v>6662168</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,7 +1031,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1033,12 +1041,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,6 +1055,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1065,10 +1074,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121226171</v>
+        <v>121221578</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,53 +1086,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618640</v>
+        <v>618702</v>
       </c>
       <c r="R5" t="n">
-        <v>6662155</v>
+        <v>6662175</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,7 +1157,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1162,12 +1167,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,7 +1181,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121225934</v>
+        <v>121226171</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,7 +1234,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,11 +1242,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1251,13 +1251,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618662</v>
+        <v>618640</v>
       </c>
       <c r="R6" t="n">
-        <v>6662205</v>
+        <v>6662155</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121226037</v>
+        <v>121225934</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618640</v>
+        <v>618662</v>
       </c>
       <c r="R7" t="n">
-        <v>6662168</v>
+        <v>6662205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1466,7 +1466,7 @@
         <v>121222114</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -940,7 +940,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121226037</v>
+        <v>121226171</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -983,11 +983,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -999,10 +995,10 @@
         <v>618640</v>
       </c>
       <c r="R4" t="n">
-        <v>6662168</v>
+        <v>6662155</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,7 +1027,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1037,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1074,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121221578</v>
+        <v>121226037</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,46 +1082,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618702</v>
+        <v>618640</v>
       </c>
       <c r="R5" t="n">
-        <v>6662175</v>
+        <v>6662168</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,7 +1161,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1167,12 +1171,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,6 +1185,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1199,10 +1204,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121226171</v>
+        <v>121221578</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>56568</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,53 +1216,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618640</v>
+        <v>618702</v>
       </c>
       <c r="R6" t="n">
-        <v>6662155</v>
+        <v>6662175</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1286,7 +1287,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1296,12 +1297,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,7 +1311,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121226171</v>
+        <v>121221578</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,53 +952,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618640</v>
+        <v>618702</v>
       </c>
       <c r="R4" t="n">
-        <v>6662155</v>
+        <v>6662175</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1027,7 +1023,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,12 +1033,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1047,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1204,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121221578</v>
+        <v>121226171</v>
       </c>
       <c r="B6" t="n">
-        <v>56568</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,49 +1211,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrvallsmossen NV om, Upl</t>
+          <t>Norrvallsmossen NV om, Norrvallsmossen NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>618702</v>
+        <v>618640</v>
       </c>
       <c r="R6" t="n">
-        <v>6662175</v>
+        <v>6662155</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1287,7 +1286,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1297,12 +1296,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre vinterkrokar under mattall, tallen står i kanten av en mindre glup.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,6 +1310,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50466-2024 artfynd.xlsx
+++ b/artfynd/A 50466-2024 artfynd.xlsx
@@ -1065,7 +1065,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121226037</v>
+        <v>121225934</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618640</v>
+        <v>618662</v>
       </c>
       <c r="R5" t="n">
-        <v>6662168</v>
+        <v>6662205</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1329,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121225934</v>
+        <v>121226037</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>618662</v>
+        <v>618640</v>
       </c>
       <c r="R7" t="n">
-        <v>6662205</v>
+        <v>6662168</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter.  Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
+          <t>Markerade med plastkäpp och pinnar i hyggesfriförsöket.</t>
         </is>
       </c>
       <c r="AD7" t="b">
